--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 835-2026 artfynd.xlsx
+++ b/artfynd/A 835-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131105811</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
